--- a/Result/profitability/5529.xlsx
+++ b/Result/profitability/5529.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2825000000000001</v>
+        <v>0.38875</v>
       </c>
       <c r="N2" t="n">
-        <v>30.07375</v>
+        <v>27.69625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,16 +780,16 @@
         <v>1.42</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5012500000000001</v>
+        <v>0.5900000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>25.98</v>
+        <v>23.13874999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.51</v>
       </c>
       <c r="M4" t="n">
-        <v>0.58875</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>22.38</v>
+        <v>24.80875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>-0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.58875</v>
+        <v>0.6837500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>23.2925</v>
+        <v>26.555</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6687500000000001</v>
+        <v>0.7625000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>23.88375</v>
+        <v>26.84624999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.09</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7087500000000001</v>
+        <v>0.43125</v>
       </c>
       <c r="N7" t="n">
-        <v>24.08624999999999</v>
+        <v>24.19125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.39</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3175</v>
+        <v>0.29875</v>
       </c>
       <c r="N8" t="n">
-        <v>20.82875</v>
+        <v>20.8275</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>258</v>
+      </c>
+      <c r="D75" t="n">
+        <v>166</v>
+      </c>
+      <c r="E75" t="n">
+        <v>92</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.78</v>
+      </c>
+      <c r="G75" t="n">
+        <v>52</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>20.33%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>12</v>
+      </c>
+      <c r="J75" t="n">
+        <v>64</v>
+      </c>
+      <c r="K75" t="n">
+        <v>55</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.3362500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.24124999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2238805970149254</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.00999999999999801</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0002794076557697256</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.166666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>2.696280991735537</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
